--- a/Reels/SanskaTots_Content.xlsx
+++ b/Reels/SanskaTots_Content.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/prashanth.mg/sourcecode/sanskatots/Reels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F690CE-7199-DD4D-9C47-6A2733D447DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D6FA34-D99F-8041-BE63-08EC5D9BE96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{FF527E2C-730C-504A-BE8C-5A0D73E14E91}"/>
+    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{FF527E2C-730C-504A-BE8C-5A0D73E14E91}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Reels" sheetId="1" r:id="rId1"/>
     <sheet name="Content Ideas" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="73">
   <si>
     <t>Instagram Reels — Content Calendar (Launch Run-Up)</t>
   </si>
@@ -269,6 +269,23 @@
   </si>
   <si>
     <t>A simple framework parents can follow.</t>
+  </si>
+  <si>
+    <t>Papa's Special Gift (Father–Daughter Bonding) — Stick Figure Animation, 45 sec</t>
+  </si>
+  <si>
+    <t>Emotional / Storytelling (Stick Figure Animation)</t>
+  </si>
+  <si>
+    <t>HOOK (0-4s) [VOICEOVER, soft piano]: "It was 10 PM. He hadn't seen his little girl in two whole days…"
+SCENE 1 (5-13s): "After endless hours at the office, exhausted… he rushed home — just to see HER. But at the door, his wife gently whispered… 'She waited for you, papa… but she just fell asleep.'"
+SCENE 2 (14-24s): "His heart sank a little. But he had something special — a gift he'd been saving for her. So quietly… so softly… he tiptoed into her room, placed it right beside her, kissed her forehead… and turned to leave."
+SCENE 3 — THE MOMENT (25-32s): "And then… a tiny sleepy voice. 'Papa…?' He turned around. And just like that — every tired bone in his body melted into the biggest smile."
+SCENE 4 (33-42s): "The next morning… pure magic. Pulling Velcro stickers, giggling, learning her animals — lost in her SanskaTots Animal Busy Book. The gift wasn't just a book… it was papa's love, in her tiny hands."
+CTA (43-45s): "Some gifts they unwrap. Some gifts they remember forever. SanskaTots Animal Busy Book — launching June 21st."</t>
+  </si>
+  <si>
+    <t>POV: He came home late just to see her… but she was already asleep 🥹</t>
   </si>
 </sst>
 </file>
@@ -397,7 +414,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -422,6 +439,19 @@
     </border>
     <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFCE93D8"/>
       </left>
       <right style="thin">
@@ -439,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -468,41 +498,56 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -842,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92111040-EDB2-B44C-B0B2-FDD45CD2A623}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
@@ -903,7 +948,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="197" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -944,22 +989,42 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="23">
         <v>46190</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="272" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="26">
+        <v>46192</v>
+      </c>
+      <c r="F8" s="25" t="s">
         <v>11</v>
       </c>
     </row>
